--- a/1_network_estimation/1_data_cleaning/Data_clean/MCAS/Estados_US/Edos_USA_2020/DELAWARE_2020.xlsx
+++ b/1_network_estimation/1_data_cleaning/Data_clean/MCAS/Estados_US/Edos_USA_2020/DELAWARE_2020.xlsx
@@ -351,28 +351,28 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D329"/>
+  <dimension ref="A1:D323"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Estado de Origen</t>
+          <t>mx_state</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Municipio Origen</t>
+          <t>mx_municipality</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Número de Matrículas</t>
+          <t>n_matriculas</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Porcentaje de Matrículas</t>
+          <t>pct_matriculas</t>
         </is>
       </c>
     </row>
@@ -395,6 +395,11 @@
       </c>
     </row>
     <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Aguascalientes</t>
+        </is>
+      </c>
       <c r="B3" t="inlineStr">
         <is>
           <t>Jesús María</t>
@@ -408,6 +413,11 @@
       </c>
     </row>
     <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Aguascalientes</t>
+        </is>
+      </c>
       <c r="B4" t="inlineStr">
         <is>
           <t>Total</t>
@@ -439,6 +449,11 @@
       </c>
     </row>
     <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Baja California</t>
+        </is>
+      </c>
       <c r="B6" t="inlineStr">
         <is>
           <t>Total</t>
@@ -459,7 +474,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Amatenango de la Frontera</t>
+          <t>Amatenango De La Frontera</t>
         </is>
       </c>
       <c r="C7">
@@ -470,6 +485,11 @@
       </c>
     </row>
     <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B8" t="inlineStr">
         <is>
           <t>Angel Albino Corzo</t>
@@ -483,9 +503,14 @@
       </c>
     </row>
     <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Bejucal de Ocampo</t>
+          <t>Bejucal De Ocampo</t>
         </is>
       </c>
       <c r="C9">
@@ -496,6 +521,11 @@
       </c>
     </row>
     <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B10" t="inlineStr">
         <is>
           <t>Cacahoatán</t>
@@ -509,6 +539,11 @@
       </c>
     </row>
     <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B11" t="inlineStr">
         <is>
           <t>El Porvenir</t>
@@ -522,6 +557,11 @@
       </c>
     </row>
     <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B12" t="inlineStr">
         <is>
           <t>Frontera Comalapa</t>
@@ -535,6 +575,11 @@
       </c>
     </row>
     <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B13" t="inlineStr">
         <is>
           <t>Huehuetán</t>
@@ -548,6 +593,11 @@
       </c>
     </row>
     <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B14" t="inlineStr">
         <is>
           <t>Huixtla</t>
@@ -561,6 +611,11 @@
       </c>
     </row>
     <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B15" t="inlineStr">
         <is>
           <t>Ixhuatán</t>
@@ -574,6 +629,11 @@
       </c>
     </row>
     <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B16" t="inlineStr">
         <is>
           <t>La Concordia</t>
@@ -587,6 +647,11 @@
       </c>
     </row>
     <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B17" t="inlineStr">
         <is>
           <t>La Grandeza</t>
@@ -600,6 +665,11 @@
       </c>
     </row>
     <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B18" t="inlineStr">
         <is>
           <t>Las Margaritas</t>
@@ -613,6 +683,11 @@
       </c>
     </row>
     <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B19" t="inlineStr">
         <is>
           <t>Motozintla</t>
@@ -626,6 +701,11 @@
       </c>
     </row>
     <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B20" t="inlineStr">
         <is>
           <t>Tapachula</t>
@@ -639,6 +719,11 @@
       </c>
     </row>
     <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B21" t="inlineStr">
         <is>
           <t>Teopisca</t>
@@ -652,6 +737,11 @@
       </c>
     </row>
     <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B22" t="inlineStr">
         <is>
           <t>Unión Juárez</t>
@@ -665,6 +755,11 @@
       </c>
     </row>
     <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B23" t="inlineStr">
         <is>
           <t>Villa Comaltitlán</t>
@@ -678,6 +773,11 @@
       </c>
     </row>
     <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B24" t="inlineStr">
         <is>
           <t>Total</t>
@@ -709,6 +809,11 @@
       </c>
     </row>
     <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B26" t="inlineStr">
         <is>
           <t>Cuauhtémoc</t>
@@ -722,9 +827,14 @@
       </c>
     </row>
     <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Hidalgo del Parral</t>
+          <t>Hidalgo Del Parral</t>
         </is>
       </c>
       <c r="C27">
@@ -735,6 +845,11 @@
       </c>
     </row>
     <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B28" t="inlineStr">
         <is>
           <t>Madera</t>
@@ -748,6 +863,11 @@
       </c>
     </row>
     <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B29" t="inlineStr">
         <is>
           <t>Total</t>
@@ -763,7 +883,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Ciudad de México</t>
+          <t>Ciudad De México</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -779,6 +899,11 @@
       </c>
     </row>
     <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B31" t="inlineStr">
         <is>
           <t>Azcapotzalco</t>
@@ -792,6 +917,11 @@
       </c>
     </row>
     <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B32" t="inlineStr">
         <is>
           <t>Coyoacán</t>
@@ -805,6 +935,11 @@
       </c>
     </row>
     <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B33" t="inlineStr">
         <is>
           <t>Cuauhtémoc</t>
@@ -818,6 +953,11 @@
       </c>
     </row>
     <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B34" t="inlineStr">
         <is>
           <t>Gustavo A. Madero</t>
@@ -831,6 +971,11 @@
       </c>
     </row>
     <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B35" t="inlineStr">
         <is>
           <t>Iztapalapa</t>
@@ -844,6 +989,11 @@
       </c>
     </row>
     <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B36" t="inlineStr">
         <is>
           <t>Total</t>
@@ -875,6 +1025,11 @@
       </c>
     </row>
     <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B38" t="inlineStr">
         <is>
           <t>Durango</t>
@@ -888,6 +1043,11 @@
       </c>
     </row>
     <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B39" t="inlineStr">
         <is>
           <t>Gómez Palacio</t>
@@ -901,6 +1061,11 @@
       </c>
     </row>
     <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B40" t="inlineStr">
         <is>
           <t>Mapimí</t>
@@ -914,9 +1079,14 @@
       </c>
     </row>
     <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Pánuco de Coronado</t>
+          <t>Pánuco De Coronado</t>
         </is>
       </c>
       <c r="C41">
@@ -927,6 +1097,11 @@
       </c>
     </row>
     <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B42" t="inlineStr">
         <is>
           <t>Total</t>
@@ -942,7 +1117,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Estado de México</t>
+          <t>Estado De México</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -958,9 +1133,14 @@
       </c>
     </row>
     <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Almoloya de Alquisiras</t>
+          <t>Almoloya De Alquisiras</t>
         </is>
       </c>
       <c r="C44">
@@ -971,9 +1151,14 @@
       </c>
     </row>
     <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Almoloya de Juárez</t>
+          <t>Almoloya De Juárez</t>
         </is>
       </c>
       <c r="C45">
@@ -984,6 +1169,11 @@
       </c>
     </row>
     <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B46" t="inlineStr">
         <is>
           <t>Amanalco</t>
@@ -997,6 +1187,11 @@
       </c>
     </row>
     <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B47" t="inlineStr">
         <is>
           <t>Amatepec</t>
@@ -1010,6 +1205,11 @@
       </c>
     </row>
     <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B48" t="inlineStr">
         <is>
           <t>Amecameca</t>
@@ -1023,6 +1223,11 @@
       </c>
     </row>
     <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B49" t="inlineStr">
         <is>
           <t>Atlautla</t>
@@ -1036,6 +1241,11 @@
       </c>
     </row>
     <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B50" t="inlineStr">
         <is>
           <t>Calimaya</t>
@@ -1049,6 +1259,11 @@
       </c>
     </row>
     <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B51" t="inlineStr">
         <is>
           <t>Chalco</t>
@@ -1062,6 +1277,11 @@
       </c>
     </row>
     <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B52" t="inlineStr">
         <is>
           <t>Coatepec Harinas</t>
@@ -1075,6 +1295,11 @@
       </c>
     </row>
     <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B53" t="inlineStr">
         <is>
           <t>Cocotitlán</t>
@@ -1088,9 +1313,14 @@
       </c>
     </row>
     <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Ecatepec de Morelos</t>
+          <t>Ecatepec De Morelos</t>
         </is>
       </c>
       <c r="C54">
@@ -1101,6 +1331,11 @@
       </c>
     </row>
     <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B55" t="inlineStr">
         <is>
           <t>Ecatzingo</t>
@@ -1114,6 +1349,11 @@
       </c>
     </row>
     <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B56" t="inlineStr">
         <is>
           <t>Ixtapaluca</t>
@@ -1127,9 +1367,14 @@
       </c>
     </row>
     <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Ixtapan de la Sal</t>
+          <t>Ixtapan De La Sal</t>
         </is>
       </c>
       <c r="C57">
@@ -1140,9 +1385,14 @@
       </c>
     </row>
     <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Ixtapan del Oro</t>
+          <t>Ixtapan Del Oro</t>
         </is>
       </c>
       <c r="C58">
@@ -1153,6 +1403,11 @@
       </c>
     </row>
     <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B59" t="inlineStr">
         <is>
           <t>Ixtlahuaca</t>
@@ -1166,6 +1421,11 @@
       </c>
     </row>
     <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B60" t="inlineStr">
         <is>
           <t>Joquicingo</t>
@@ -1179,6 +1439,11 @@
       </c>
     </row>
     <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B61" t="inlineStr">
         <is>
           <t>La Paz</t>
@@ -1192,6 +1457,11 @@
       </c>
     </row>
     <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B62" t="inlineStr">
         <is>
           <t>Malinalco</t>
@@ -1205,9 +1475,14 @@
       </c>
     </row>
     <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Naucalpan de Juárez</t>
+          <t>Naucalpan De Juárez</t>
         </is>
       </c>
       <c r="C63">
@@ -1218,6 +1493,11 @@
       </c>
     </row>
     <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B64" t="inlineStr">
         <is>
           <t>Nezahualcóyotl</t>
@@ -1231,6 +1511,11 @@
       </c>
     </row>
     <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B65" t="inlineStr">
         <is>
           <t>Ocoyoacac</t>
@@ -1244,9 +1529,14 @@
       </c>
     </row>
     <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>San Felipe del Progreso</t>
+          <t>San Felipe Del Progreso</t>
         </is>
       </c>
       <c r="C66">
@@ -1257,9 +1547,14 @@
       </c>
     </row>
     <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>San Martín de las Pirámides</t>
+          <t>San Martín De Las Pirámides</t>
         </is>
       </c>
       <c r="C67">
@@ -1270,9 +1565,14 @@
       </c>
     </row>
     <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>San Simón de Guerero</t>
+          <t>San Simón De Guerero</t>
         </is>
       </c>
       <c r="C68">
@@ -1283,6 +1583,11 @@
       </c>
     </row>
     <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B69" t="inlineStr">
         <is>
           <t>Sultepec</t>
@@ -1296,6 +1601,11 @@
       </c>
     </row>
     <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B70" t="inlineStr">
         <is>
           <t>Temascaltepec</t>
@@ -1309,6 +1619,11 @@
       </c>
     </row>
     <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B71" t="inlineStr">
         <is>
           <t>Temoaya</t>
@@ -1322,6 +1637,11 @@
       </c>
     </row>
     <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B72" t="inlineStr">
         <is>
           <t>Tenancingo</t>
@@ -1335,9 +1655,14 @@
       </c>
     </row>
     <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Tenango del Valle</t>
+          <t>Tenango Del Valle</t>
         </is>
       </c>
       <c r="C73">
@@ -1348,6 +1673,11 @@
       </c>
     </row>
     <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B74" t="inlineStr">
         <is>
           <t>Tepetlaoxtoc</t>
@@ -1361,6 +1691,11 @@
       </c>
     </row>
     <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B75" t="inlineStr">
         <is>
           <t>Tepotzotlán</t>
@@ -1374,6 +1709,11 @@
       </c>
     </row>
     <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B76" t="inlineStr">
         <is>
           <t>Texcaltitlán</t>
@@ -1387,6 +1727,11 @@
       </c>
     </row>
     <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B77" t="inlineStr">
         <is>
           <t>Texcoco</t>
@@ -1400,9 +1745,14 @@
       </c>
     </row>
     <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Tlalnepantla de Baz</t>
+          <t>Tlalnepantla De Baz</t>
         </is>
       </c>
       <c r="C78">
@@ -1413,6 +1763,11 @@
       </c>
     </row>
     <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B79" t="inlineStr">
         <is>
           <t>Toluca</t>
@@ -1426,6 +1781,11 @@
       </c>
     </row>
     <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B80" t="inlineStr">
         <is>
           <t>Tultitlán</t>
@@ -1439,9 +1799,14 @@
       </c>
     </row>
     <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Valle de Bravo</t>
+          <t>Valle De Bravo</t>
         </is>
       </c>
       <c r="C81">
@@ -1452,9 +1817,14 @@
       </c>
     </row>
     <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Valle de Chalco Solidaridad</t>
+          <t>Valle De Chalco Solidaridad</t>
         </is>
       </c>
       <c r="C82">
@@ -1465,6 +1835,11 @@
       </c>
     </row>
     <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B83" t="inlineStr">
         <is>
           <t>Villa Guerero</t>
@@ -1478,6 +1853,11 @@
       </c>
     </row>
     <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B84" t="inlineStr">
         <is>
           <t>Zacualpan</t>
@@ -1491,6 +1871,11 @@
       </c>
     </row>
     <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B85" t="inlineStr">
         <is>
           <t>Zinacantepec</t>
@@ -1504,6 +1889,11 @@
       </c>
     </row>
     <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B86" t="inlineStr">
         <is>
           <t>Zumpahuacán</t>
@@ -1517,6 +1907,11 @@
       </c>
     </row>
     <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B87" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1532,7 +1927,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>GUANAJUATO</t>
+          <t>Guanajuato</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -1548,6 +1943,11 @@
       </c>
     </row>
     <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B89" t="inlineStr">
         <is>
           <t>Celaya</t>
@@ -1561,6 +1961,11 @@
       </c>
     </row>
     <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B90" t="inlineStr">
         <is>
           <t>Irapuato</t>
@@ -1574,6 +1979,11 @@
       </c>
     </row>
     <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B91" t="inlineStr">
         <is>
           <t>León</t>
@@ -1587,6 +1997,11 @@
       </c>
     </row>
     <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B92" t="inlineStr">
         <is>
           <t>Manuel Doblado</t>
@@ -1600,6 +2015,11 @@
       </c>
     </row>
     <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B93" t="inlineStr">
         <is>
           <t>Moroleón</t>
@@ -1613,6 +2033,11 @@
       </c>
     </row>
     <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B94" t="inlineStr">
         <is>
           <t>Pénjamo</t>
@@ -1626,6 +2051,11 @@
       </c>
     </row>
     <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B95" t="inlineStr">
         <is>
           <t>Salvatierra</t>
@@ -1639,6 +2069,11 @@
       </c>
     </row>
     <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B96" t="inlineStr">
         <is>
           <t>Uriangato</t>
@@ -1652,6 +2087,11 @@
       </c>
     </row>
     <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B97" t="inlineStr">
         <is>
           <t>Yuriria</t>
@@ -1690,7 +2130,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Acapulco de Juárez</t>
+          <t>Acapulco De Juárez</t>
         </is>
       </c>
       <c r="C99">
@@ -1701,9 +2141,14 @@
       </c>
     </row>
     <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Guerero</t>
+        </is>
+      </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Ajuchitlán del Progreso</t>
+          <t>Ajuchitlán Del Progreso</t>
         </is>
       </c>
       <c r="C100">
@@ -1714,6 +2159,11 @@
       </c>
     </row>
     <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Guerero</t>
+        </is>
+      </c>
       <c r="B101" t="inlineStr">
         <is>
           <t>Arcelia</t>
@@ -1727,9 +2177,14 @@
       </c>
     </row>
     <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Guerero</t>
+        </is>
+      </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Ayutla de los Libres</t>
+          <t>Ayutla De Los Libres</t>
         </is>
       </c>
       <c r="C102">
@@ -1740,9 +2195,14 @@
       </c>
     </row>
     <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Guerero</t>
+        </is>
+      </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Chilapa de Álvarez</t>
+          <t>Chilapa De Álvarez</t>
         </is>
       </c>
       <c r="C103">
@@ -1753,9 +2213,14 @@
       </c>
     </row>
     <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Guerero</t>
+        </is>
+      </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Coahuayutla de José María Izazaga</t>
+          <t>Coahuayutla De José María Izazaga</t>
         </is>
       </c>
       <c r="C104">
@@ -1766,9 +2231,14 @@
       </c>
     </row>
     <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Guerero</t>
+        </is>
+      </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Coyuca de Catalán</t>
+          <t>Coyuca De Catalán</t>
         </is>
       </c>
       <c r="C105">
@@ -1779,6 +2249,11 @@
       </c>
     </row>
     <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Guerero</t>
+        </is>
+      </c>
       <c r="B106" t="inlineStr">
         <is>
           <t>Florencio Villarreal</t>
@@ -1792,6 +2267,11 @@
       </c>
     </row>
     <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Guerero</t>
+        </is>
+      </c>
       <c r="B107" t="inlineStr">
         <is>
           <t>General Canuto A. Neri</t>
@@ -1805,6 +2285,11 @@
       </c>
     </row>
     <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Guerero</t>
+        </is>
+      </c>
       <c r="B108" t="inlineStr">
         <is>
           <t>General Heliodoro Castillo</t>
@@ -1818,9 +2303,14 @@
       </c>
     </row>
     <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Guerero</t>
+        </is>
+      </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Huitzuco de los Figueroa</t>
+          <t>Huitzuco De Los Figueroa</t>
         </is>
       </c>
       <c r="C109">
@@ -1831,9 +2321,14 @@
       </c>
     </row>
     <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Guerero</t>
+        </is>
+      </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Iguala de la Independencia</t>
+          <t>Iguala De La Independencia</t>
         </is>
       </c>
       <c r="C110">
@@ -1844,9 +2339,14 @@
       </c>
     </row>
     <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Guerero</t>
+        </is>
+      </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Zihuatanejo de Azueta</t>
+          <t>Zihuatanejo De Azueta</t>
         </is>
       </c>
       <c r="C111">
@@ -1857,6 +2357,11 @@
       </c>
     </row>
     <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Guerero</t>
+        </is>
+      </c>
       <c r="B112" t="inlineStr">
         <is>
           <t>Juan R. Escudero</t>
@@ -1870,6 +2375,11 @@
       </c>
     </row>
     <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Guerero</t>
+        </is>
+      </c>
       <c r="B113" t="inlineStr">
         <is>
           <t>Leonardo Bravo</t>
@@ -1883,6 +2393,11 @@
       </c>
     </row>
     <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Guerero</t>
+        </is>
+      </c>
       <c r="B114" t="inlineStr">
         <is>
           <t>Olinalá</t>
@@ -1896,6 +2411,11 @@
       </c>
     </row>
     <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Guerero</t>
+        </is>
+      </c>
       <c r="B115" t="inlineStr">
         <is>
           <t>Pedro Ascencio Alquisiras</t>
@@ -1909,6 +2429,11 @@
       </c>
     </row>
     <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Guerero</t>
+        </is>
+      </c>
       <c r="B116" t="inlineStr">
         <is>
           <t>Pilcaya</t>
@@ -1922,9 +2447,14 @@
       </c>
     </row>
     <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Guerero</t>
+        </is>
+      </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Taxco de Alarcón</t>
+          <t>Taxco De Alarcón</t>
         </is>
       </c>
       <c r="C117">
@@ -1935,6 +2465,11 @@
       </c>
     </row>
     <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Guerero</t>
+        </is>
+      </c>
       <c r="B118" t="inlineStr">
         <is>
           <t>Teloloapan</t>
@@ -1948,9 +2483,14 @@
       </c>
     </row>
     <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Guerero</t>
+        </is>
+      </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Tepecoacuilco de Trujano</t>
+          <t>Tepecoacuilco De Trujano</t>
         </is>
       </c>
       <c r="C119">
@@ -1961,6 +2501,11 @@
       </c>
     </row>
     <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Guerero</t>
+        </is>
+      </c>
       <c r="B120" t="inlineStr">
         <is>
           <t>Tetipac</t>
@@ -1974,6 +2519,11 @@
       </c>
     </row>
     <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Guerero</t>
+        </is>
+      </c>
       <c r="B121" t="inlineStr">
         <is>
           <t>Tlacoachistlahuaca</t>
@@ -1987,6 +2537,11 @@
       </c>
     </row>
     <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Guerero</t>
+        </is>
+      </c>
       <c r="B122" t="inlineStr">
         <is>
           <t>Zirándaro</t>
@@ -2000,6 +2555,11 @@
       </c>
     </row>
     <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Guerero</t>
+        </is>
+      </c>
       <c r="B123" t="inlineStr">
         <is>
           <t>Total</t>
@@ -2031,9 +2591,14 @@
       </c>
     </row>
     <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Tulancingo de Bravo</t>
+          <t>Tulancingo De Bravo</t>
         </is>
       </c>
       <c r="C125">
@@ -2044,6 +2609,11 @@
       </c>
     </row>
     <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B126" t="inlineStr">
         <is>
           <t>Total</t>
@@ -2064,7 +2634,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Ahualulco de Mercado</t>
+          <t>Ahualulco De Mercado</t>
         </is>
       </c>
       <c r="C127">
@@ -2075,6 +2645,11 @@
       </c>
     </row>
     <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B128" t="inlineStr">
         <is>
           <t>Chapala</t>
@@ -2088,6 +2663,11 @@
       </c>
     </row>
     <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B129" t="inlineStr">
         <is>
           <t>Cuquío</t>
@@ -2101,6 +2681,11 @@
       </c>
     </row>
     <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B130" t="inlineStr">
         <is>
           <t>El Salto</t>
@@ -2114,9 +2699,14 @@
       </c>
     </row>
     <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Encarnación de Díaz</t>
+          <t>Encarnación De Díaz</t>
         </is>
       </c>
       <c r="C131">
@@ -2127,6 +2717,11 @@
       </c>
     </row>
     <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B132" t="inlineStr">
         <is>
           <t>Guadalajara</t>
@@ -2140,6 +2735,11 @@
       </c>
     </row>
     <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B133" t="inlineStr">
         <is>
           <t>Jalostotitlán</t>
@@ -2153,9 +2753,14 @@
       </c>
     </row>
     <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Lagos de Moreno</t>
+          <t>Lagos De Moreno</t>
         </is>
       </c>
       <c r="C134">
@@ -2166,6 +2771,11 @@
       </c>
     </row>
     <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B135" t="inlineStr">
         <is>
           <t>Puerto Vallarta</t>
@@ -2179,9 +2789,14 @@
       </c>
     </row>
     <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Tizapán el Alto</t>
+          <t>Tizapán El Alto</t>
         </is>
       </c>
       <c r="C136">
@@ -2192,6 +2807,11 @@
       </c>
     </row>
     <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B137" t="inlineStr">
         <is>
           <t>Zapopan</t>
@@ -2205,6 +2825,11 @@
       </c>
     </row>
     <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B138" t="inlineStr">
         <is>
           <t>Zapotlanejo</t>
@@ -2218,6 +2843,11 @@
       </c>
     </row>
     <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B139" t="inlineStr">
         <is>
           <t>Total</t>
@@ -2249,6 +2879,11 @@
       </c>
     </row>
     <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B141" t="inlineStr">
         <is>
           <t>Ario</t>
@@ -2262,6 +2897,11 @@
       </c>
     </row>
     <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B142" t="inlineStr">
         <is>
           <t>Carácuaro</t>
@@ -2275,6 +2915,11 @@
       </c>
     </row>
     <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B143" t="inlineStr">
         <is>
           <t>Chavinda</t>
@@ -2288,6 +2933,11 @@
       </c>
     </row>
     <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B144" t="inlineStr">
         <is>
           <t>Coeneo</t>
@@ -2301,6 +2951,11 @@
       </c>
     </row>
     <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B145" t="inlineStr">
         <is>
           <t>Erongarícuaro</t>
@@ -2314,6 +2969,11 @@
       </c>
     </row>
     <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B146" t="inlineStr">
         <is>
           <t>Gabriel Zamora</t>
@@ -2327,6 +2987,11 @@
       </c>
     </row>
     <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B147" t="inlineStr">
         <is>
           <t>Huetamo</t>
@@ -2340,6 +3005,11 @@
       </c>
     </row>
     <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B148" t="inlineStr">
         <is>
           <t>La Huacana</t>
@@ -2353,6 +3023,11 @@
       </c>
     </row>
     <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B149" t="inlineStr">
         <is>
           <t>Lázaro Cárdenas</t>
@@ -2366,6 +3041,11 @@
       </c>
     </row>
     <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B150" t="inlineStr">
         <is>
           <t>Morelia</t>
@@ -2379,6 +3059,11 @@
       </c>
     </row>
     <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B151" t="inlineStr">
         <is>
           <t>Múgica</t>
@@ -2392,6 +3077,11 @@
       </c>
     </row>
     <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B152" t="inlineStr">
         <is>
           <t>Nahuatzen</t>
@@ -2405,6 +3095,11 @@
       </c>
     </row>
     <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B153" t="inlineStr">
         <is>
           <t>Nocupétaro</t>
@@ -2418,6 +3113,11 @@
       </c>
     </row>
     <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B154" t="inlineStr">
         <is>
           <t>Ocampo</t>
@@ -2431,6 +3131,11 @@
       </c>
     </row>
     <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B155" t="inlineStr">
         <is>
           <t>Pátzcuaro</t>
@@ -2444,6 +3149,11 @@
       </c>
     </row>
     <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B156" t="inlineStr">
         <is>
           <t>Puruándiro</t>
@@ -2457,6 +3167,11 @@
       </c>
     </row>
     <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B157" t="inlineStr">
         <is>
           <t>Quiroga</t>
@@ -2470,6 +3185,11 @@
       </c>
     </row>
     <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B158" t="inlineStr">
         <is>
           <t>San Lucas</t>
@@ -2483,6 +3203,11 @@
       </c>
     </row>
     <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B159" t="inlineStr">
         <is>
           <t>Tacámbaro</t>
@@ -2496,6 +3221,11 @@
       </c>
     </row>
     <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B160" t="inlineStr">
         <is>
           <t>Tangamandapio</t>
@@ -2509,6 +3239,11 @@
       </c>
     </row>
     <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B161" t="inlineStr">
         <is>
           <t>Uruapan</t>
@@ -2522,6 +3257,11 @@
       </c>
     </row>
     <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B162" t="inlineStr">
         <is>
           <t>Zacapu</t>
@@ -2535,6 +3275,11 @@
       </c>
     </row>
     <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B163" t="inlineStr">
         <is>
           <t>Zamora</t>
@@ -2548,6 +3293,11 @@
       </c>
     </row>
     <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B164" t="inlineStr">
         <is>
           <t>Zinapécuaro</t>
@@ -2561,6 +3311,11 @@
       </c>
     </row>
     <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B165" t="inlineStr">
         <is>
           <t>Zitácuaro</t>
@@ -2574,6 +3329,11 @@
       </c>
     </row>
     <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B166" t="inlineStr">
         <is>
           <t>Total</t>
@@ -2605,6 +3365,11 @@
       </c>
     </row>
     <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B168" t="inlineStr">
         <is>
           <t>Axochiapan</t>
@@ -2618,6 +3383,11 @@
       </c>
     </row>
     <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B169" t="inlineStr">
         <is>
           <t>Cuautla</t>
@@ -2631,6 +3401,11 @@
       </c>
     </row>
     <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B170" t="inlineStr">
         <is>
           <t>Cuernavaca</t>
@@ -2644,6 +3419,11 @@
       </c>
     </row>
     <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B171" t="inlineStr">
         <is>
           <t>Jiutepec</t>
@@ -2657,6 +3437,11 @@
       </c>
     </row>
     <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B172" t="inlineStr">
         <is>
           <t>Jojutla</t>
@@ -2670,9 +3455,14 @@
       </c>
     </row>
     <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Puente de Ixtla</t>
+          <t>Puente De Ixtla</t>
         </is>
       </c>
       <c r="C173">
@@ -2683,6 +3473,11 @@
       </c>
     </row>
     <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B174" t="inlineStr">
         <is>
           <t>Temixco</t>
@@ -2696,6 +3491,11 @@
       </c>
     </row>
     <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B175" t="inlineStr">
         <is>
           <t>Tetecala</t>
@@ -2709,9 +3509,14 @@
       </c>
     </row>
     <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Tlaltizapán de Zapata</t>
+          <t>Tlaltizapán De Zapata</t>
         </is>
       </c>
       <c r="C176">
@@ -2722,6 +3527,11 @@
       </c>
     </row>
     <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B177" t="inlineStr">
         <is>
           <t>Tlaquiltenango</t>
@@ -2735,6 +3545,11 @@
       </c>
     </row>
     <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B178" t="inlineStr">
         <is>
           <t>Tlayacapan</t>
@@ -2748,6 +3563,11 @@
       </c>
     </row>
     <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B179" t="inlineStr">
         <is>
           <t>Yautepec</t>
@@ -2761,6 +3581,11 @@
       </c>
     </row>
     <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B180" t="inlineStr">
         <is>
           <t>Zacatepec</t>
@@ -2774,6 +3599,11 @@
       </c>
     </row>
     <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B181" t="inlineStr">
         <is>
           <t>Total</t>
@@ -2805,9 +3635,14 @@
       </c>
     </row>
     <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>Nayarit</t>
+        </is>
+      </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Ixtlán del Río</t>
+          <t>Ixtlán Del Río</t>
         </is>
       </c>
       <c r="C183">
@@ -2818,6 +3653,11 @@
       </c>
     </row>
     <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>Nayarit</t>
+        </is>
+      </c>
       <c r="B184" t="inlineStr">
         <is>
           <t>La Yesca</t>
@@ -2831,6 +3671,11 @@
       </c>
     </row>
     <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>Nayarit</t>
+        </is>
+      </c>
       <c r="B185" t="inlineStr">
         <is>
           <t>Rosamorada</t>
@@ -2844,6 +3689,11 @@
       </c>
     </row>
     <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>Nayarit</t>
+        </is>
+      </c>
       <c r="B186" t="inlineStr">
         <is>
           <t>Tepic</t>
@@ -2857,6 +3707,11 @@
       </c>
     </row>
     <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>Nayarit</t>
+        </is>
+      </c>
       <c r="B187" t="inlineStr">
         <is>
           <t>Total</t>
@@ -2888,6 +3743,11 @@
       </c>
     </row>
     <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B189" t="inlineStr">
         <is>
           <t>Nuevo Zoquiápam</t>
@@ -2901,9 +3761,14 @@
       </c>
     </row>
     <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Oaxaca de Juárez</t>
+          <t>Oaxaca De Juárez</t>
         </is>
       </c>
       <c r="C190">
@@ -2914,6 +3779,11 @@
       </c>
     </row>
     <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B191" t="inlineStr">
         <is>
           <t>San Andrés Cabecera Nueva</t>
@@ -2927,9 +3797,14 @@
       </c>
     </row>
     <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>San Dionisio del Mar</t>
+          <t>San Dionisio Del Mar</t>
         </is>
       </c>
       <c r="C192">
@@ -2940,6 +3815,11 @@
       </c>
     </row>
     <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B193" t="inlineStr">
         <is>
           <t>San Gabriel Mixtepec</t>
@@ -2953,6 +3833,11 @@
       </c>
     </row>
     <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B194" t="inlineStr">
         <is>
           <t>San Juan Bautista Tuxtepec</t>
@@ -2966,6 +3851,11 @@
       </c>
     </row>
     <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B195" t="inlineStr">
         <is>
           <t>San Juan Quiahije</t>
@@ -2979,6 +3869,11 @@
       </c>
     </row>
     <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B196" t="inlineStr">
         <is>
           <t>San Juan Teitipac</t>
@@ -2992,6 +3887,11 @@
       </c>
     </row>
     <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B197" t="inlineStr">
         <is>
           <t>San Juan Tepeuxila</t>
@@ -3005,6 +3905,11 @@
       </c>
     </row>
     <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B198" t="inlineStr">
         <is>
           <t>San Juan Yatzona</t>
@@ -3018,6 +3923,11 @@
       </c>
     </row>
     <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B199" t="inlineStr">
         <is>
           <t>San Lucas Ojitlán</t>
@@ -3031,6 +3941,11 @@
       </c>
     </row>
     <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B200" t="inlineStr">
         <is>
           <t>San Miguel Quetzaltepec</t>
@@ -3044,6 +3959,11 @@
       </c>
     </row>
     <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B201" t="inlineStr">
         <is>
           <t>San Miguel Tequixtepec</t>
@@ -3057,6 +3977,11 @@
       </c>
     </row>
     <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B202" t="inlineStr">
         <is>
           <t>San Sebastián Abasolo</t>
@@ -3070,6 +3995,11 @@
       </c>
     </row>
     <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B203" t="inlineStr">
         <is>
           <t>Santiago Jocotepec</t>
@@ -3083,6 +4013,11 @@
       </c>
     </row>
     <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B204" t="inlineStr">
         <is>
           <t>Santiago Juxtlahuaca</t>
@@ -3096,6 +4031,11 @@
       </c>
     </row>
     <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B205" t="inlineStr">
         <is>
           <t>Santo Domingo Tehuantepec</t>
@@ -3109,6 +4049,11 @@
       </c>
     </row>
     <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B206" t="inlineStr">
         <is>
           <t>Santo Domingo Tepuxtepec</t>
@@ -3122,6 +4067,11 @@
       </c>
     </row>
     <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B207" t="inlineStr">
         <is>
           <t>Santo Domingo Tonalá</t>
@@ -3135,6 +4085,11 @@
       </c>
     </row>
     <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B208" t="inlineStr">
         <is>
           <t>Santo Domingo Zanatepec</t>
@@ -3148,6 +4103,11 @@
       </c>
     </row>
     <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B209" t="inlineStr">
         <is>
           <t>Silacayoápam</t>
@@ -3161,9 +4121,14 @@
       </c>
     </row>
     <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>Tlacolula de Matamoros</t>
+          <t>Tlacolula De Matamoros</t>
         </is>
       </c>
       <c r="C210">
@@ -3174,9 +4139,14 @@
       </c>
     </row>
     <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>Villa de Tututepec de Melchor Ocampo</t>
+          <t>Villa De Tututepec De Melchor Ocampo</t>
         </is>
       </c>
       <c r="C211">
@@ -3187,6 +4157,11 @@
       </c>
     </row>
     <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B212" t="inlineStr">
         <is>
           <t>Total</t>
@@ -3218,6 +4193,11 @@
       </c>
     </row>
     <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B214" t="inlineStr">
         <is>
           <t>Ajalpan</t>
@@ -3231,6 +4211,11 @@
       </c>
     </row>
     <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B215" t="inlineStr">
         <is>
           <t>Atlixco</t>
@@ -3244,9 +4229,14 @@
       </c>
     </row>
     <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>Ayotoxco de Guerero</t>
+          <t>Ayotoxco De Guerero</t>
         </is>
       </c>
       <c r="C216">
@@ -3257,6 +4247,11 @@
       </c>
     </row>
     <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B217" t="inlineStr">
         <is>
           <t>Calpan</t>
@@ -3270,6 +4265,11 @@
       </c>
     </row>
     <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B218" t="inlineStr">
         <is>
           <t>Chapulco</t>
@@ -3283,6 +4283,11 @@
       </c>
     </row>
     <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B219" t="inlineStr">
         <is>
           <t>Chiautla</t>
@@ -3296,6 +4301,11 @@
       </c>
     </row>
     <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B220" t="inlineStr">
         <is>
           <t>Chichiquila</t>
@@ -3309,6 +4319,11 @@
       </c>
     </row>
     <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B221" t="inlineStr">
         <is>
           <t>Chietla</t>
@@ -3322,6 +4337,11 @@
       </c>
     </row>
     <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B222" t="inlineStr">
         <is>
           <t>Cohetzala</t>
@@ -3335,9 +4355,14 @@
       </c>
     </row>
     <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>Cuetzalan del Progreso</t>
+          <t>Cuetzalan Del Progreso</t>
         </is>
       </c>
       <c r="C223">
@@ -3348,6 +4373,11 @@
       </c>
     </row>
     <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B224" t="inlineStr">
         <is>
           <t>Domingo Arenas</t>
@@ -3361,6 +4391,11 @@
       </c>
     </row>
     <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B225" t="inlineStr">
         <is>
           <t>Hermenegildo Galeana</t>
@@ -3374,6 +4409,11 @@
       </c>
     </row>
     <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B226" t="inlineStr">
         <is>
           <t>Huaquechula</t>
@@ -3387,6 +4427,11 @@
       </c>
     </row>
     <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B227" t="inlineStr">
         <is>
           <t>Huauchinango</t>
@@ -3400,6 +4445,11 @@
       </c>
     </row>
     <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B228" t="inlineStr">
         <is>
           <t>Huehuetla</t>
@@ -3413,9 +4463,14 @@
       </c>
     </row>
     <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>Huehuetlán el Chico</t>
+          <t>Huehuetlán El Chico</t>
         </is>
       </c>
       <c r="C229">
@@ -3426,6 +4481,11 @@
       </c>
     </row>
     <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B230" t="inlineStr">
         <is>
           <t>Huejotzingo</t>
@@ -3439,9 +4499,14 @@
       </c>
     </row>
     <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>Izúcar de Matamoros</t>
+          <t>Izúcar De Matamoros</t>
         </is>
       </c>
       <c r="C231">
@@ -3452,6 +4517,11 @@
       </c>
     </row>
     <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B232" t="inlineStr">
         <is>
           <t>Libres</t>
@@ -3465,6 +4535,11 @@
       </c>
     </row>
     <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B233" t="inlineStr">
         <is>
           <t>Puebla</t>
@@ -3478,6 +4553,11 @@
       </c>
     </row>
     <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B234" t="inlineStr">
         <is>
           <t>Quecholac</t>
@@ -3491,6 +4571,11 @@
       </c>
     </row>
     <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B235" t="inlineStr">
         <is>
           <t>San Jerónimo Xayacatlán</t>
@@ -3504,6 +4589,11 @@
       </c>
     </row>
     <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B236" t="inlineStr">
         <is>
           <t>San Martín Texmelucan</t>
@@ -3517,6 +4607,11 @@
       </c>
     </row>
     <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B237" t="inlineStr">
         <is>
           <t>San Pablo Anicano</t>
@@ -3530,9 +4625,14 @@
       </c>
     </row>
     <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>Tecali de Herrera</t>
+          <t>Tecali De Herrera</t>
         </is>
       </c>
       <c r="C238">
@@ -3543,6 +4643,11 @@
       </c>
     </row>
     <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B239" t="inlineStr">
         <is>
           <t>Tecamachalco</t>
@@ -3556,6 +4661,11 @@
       </c>
     </row>
     <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B240" t="inlineStr">
         <is>
           <t>Teopantlán</t>
@@ -3569,6 +4679,11 @@
       </c>
     </row>
     <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B241" t="inlineStr">
         <is>
           <t>Tepeojuma</t>
@@ -3582,6 +4697,11 @@
       </c>
     </row>
     <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B242" t="inlineStr">
         <is>
           <t>Tilapa</t>
@@ -3595,9 +4715,14 @@
       </c>
     </row>
     <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>Tlacotepec de Benito Juárez</t>
+          <t>Tlacotepec De Benito Juárez</t>
         </is>
       </c>
       <c r="C243">
@@ -3608,6 +4733,11 @@
       </c>
     </row>
     <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B244" t="inlineStr">
         <is>
           <t>Tlahuapan</t>
@@ -3621,6 +4751,11 @@
       </c>
     </row>
     <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B245" t="inlineStr">
         <is>
           <t>Xicotlán</t>
@@ -3634,6 +4769,11 @@
       </c>
     </row>
     <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B246" t="inlineStr">
         <is>
           <t>Zacapoaxtla</t>
@@ -3647,6 +4787,11 @@
       </c>
     </row>
     <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B247" t="inlineStr">
         <is>
           <t>Zautla</t>
@@ -3660,6 +4805,11 @@
       </c>
     </row>
     <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B248" t="inlineStr">
         <is>
           <t>Zoquitlán</t>
@@ -3673,6 +4823,11 @@
       </c>
     </row>
     <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B249" t="inlineStr">
         <is>
           <t>Total</t>
@@ -3693,7 +4848,7 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Cadereyta de Montes</t>
+          <t>Cadereyta De Montes</t>
         </is>
       </c>
       <c r="C250">
@@ -3704,6 +4859,11 @@
       </c>
     </row>
     <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>Querétaro</t>
+        </is>
+      </c>
       <c r="B251" t="inlineStr">
         <is>
           <t>El Marqués</t>
@@ -3717,6 +4877,11 @@
       </c>
     </row>
     <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>Querétaro</t>
+        </is>
+      </c>
       <c r="B252" t="inlineStr">
         <is>
           <t>Ezequiel Montes</t>
@@ -3730,9 +4895,14 @@
       </c>
     </row>
     <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>Querétaro</t>
+        </is>
+      </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>Pinal de Amoles</t>
+          <t>Pinal De Amoles</t>
         </is>
       </c>
       <c r="C253">
@@ -3743,6 +4913,11 @@
       </c>
     </row>
     <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>Querétaro</t>
+        </is>
+      </c>
       <c r="B254" t="inlineStr">
         <is>
           <t>Querétaro</t>
@@ -3756,6 +4931,11 @@
       </c>
     </row>
     <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>Querétaro</t>
+        </is>
+      </c>
       <c r="B255" t="inlineStr">
         <is>
           <t>Total</t>
@@ -3776,7 +4956,7 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>Ciudad del Maíz</t>
+          <t>Ciudad Del Maíz</t>
         </is>
       </c>
       <c r="C256">
@@ -3787,6 +4967,11 @@
       </c>
     </row>
     <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B257" t="inlineStr">
         <is>
           <t>Ebano</t>
@@ -3800,6 +4985,11 @@
       </c>
     </row>
     <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B258" t="inlineStr">
         <is>
           <t>Rioverde</t>
@@ -3813,6 +5003,11 @@
       </c>
     </row>
     <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B259" t="inlineStr">
         <is>
           <t>Tamasopo</t>
@@ -3826,6 +5021,11 @@
       </c>
     </row>
     <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B260" t="inlineStr">
         <is>
           <t>Tampamolón Corona</t>
@@ -3839,6 +5039,11 @@
       </c>
     </row>
     <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B261" t="inlineStr">
         <is>
           <t>Total</t>
@@ -3870,6 +5075,11 @@
       </c>
     </row>
     <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>Sonora</t>
+        </is>
+      </c>
       <c r="B263" t="inlineStr">
         <is>
           <t>Total</t>
@@ -3901,6 +5111,11 @@
       </c>
     </row>
     <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>Tabasco</t>
+        </is>
+      </c>
       <c r="B265" t="inlineStr">
         <is>
           <t>Centro</t>
@@ -3914,6 +5129,11 @@
       </c>
     </row>
     <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>Tabasco</t>
+        </is>
+      </c>
       <c r="B266" t="inlineStr">
         <is>
           <t>Cunduacán</t>
@@ -3927,6 +5147,11 @@
       </c>
     </row>
     <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>Tabasco</t>
+        </is>
+      </c>
       <c r="B267" t="inlineStr">
         <is>
           <t>Huimanguillo</t>
@@ -3940,9 +5165,14 @@
       </c>
     </row>
     <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>Tabasco</t>
+        </is>
+      </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>Jalpa de Méndez</t>
+          <t>Jalpa De Méndez</t>
         </is>
       </c>
       <c r="C268">
@@ -3953,6 +5183,11 @@
       </c>
     </row>
     <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>Tabasco</t>
+        </is>
+      </c>
       <c r="B269" t="inlineStr">
         <is>
           <t>Macuspana</t>
@@ -3966,6 +5201,11 @@
       </c>
     </row>
     <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>Tabasco</t>
+        </is>
+      </c>
       <c r="B270" t="inlineStr">
         <is>
           <t>Paraíso</t>
@@ -3979,6 +5219,11 @@
       </c>
     </row>
     <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>Tabasco</t>
+        </is>
+      </c>
       <c r="B271" t="inlineStr">
         <is>
           <t>Total</t>
@@ -4010,6 +5255,11 @@
       </c>
     </row>
     <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B273" t="inlineStr">
         <is>
           <t>Reynosa</t>
@@ -4023,6 +5273,11 @@
       </c>
     </row>
     <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B274" t="inlineStr">
         <is>
           <t>Río Bravo</t>
@@ -4036,6 +5291,11 @@
       </c>
     </row>
     <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B275" t="inlineStr">
         <is>
           <t>Total</t>
@@ -4067,6 +5327,11 @@
       </c>
     </row>
     <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B277" t="inlineStr">
         <is>
           <t>Natívitas</t>
@@ -4080,6 +5345,11 @@
       </c>
     </row>
     <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B278" t="inlineStr">
         <is>
           <t>Xaloztoc</t>
@@ -4093,6 +5363,11 @@
       </c>
     </row>
     <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B279" t="inlineStr">
         <is>
           <t>Total</t>
@@ -4124,6 +5399,11 @@
       </c>
     </row>
     <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B281" t="inlineStr">
         <is>
           <t>Alvarado</t>
@@ -4137,6 +5417,11 @@
       </c>
     </row>
     <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B282" t="inlineStr">
         <is>
           <t>Atoyac</t>
@@ -4150,6 +5435,11 @@
       </c>
     </row>
     <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B283" t="inlineStr">
         <is>
           <t>Atzalan</t>
@@ -4163,9 +5453,14 @@
       </c>
     </row>
     <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>Boca del Río</t>
+          <t>Boca Del Río</t>
         </is>
       </c>
       <c r="C284">
@@ -4176,6 +5471,11 @@
       </c>
     </row>
     <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B285" t="inlineStr">
         <is>
           <t>Carrillo Puerto</t>
@@ -4189,9 +5489,14 @@
       </c>
     </row>
     <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>Cazones de Herrera</t>
+          <t>Cazones De Herrera</t>
         </is>
       </c>
       <c r="C286">
@@ -4202,6 +5507,11 @@
       </c>
     </row>
     <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B287" t="inlineStr">
         <is>
           <t>Chacaltianguis</t>
@@ -4215,6 +5525,11 @@
       </c>
     </row>
     <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B288" t="inlineStr">
         <is>
           <t>Córdoba</t>
@@ -4228,9 +5543,14 @@
       </c>
     </row>
     <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>Cosamaloapan de Carpio</t>
+          <t>Cosamaloapan De Carpio</t>
         </is>
       </c>
       <c r="C289">
@@ -4241,6 +5561,11 @@
       </c>
     </row>
     <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B290" t="inlineStr">
         <is>
           <t>Cuitláhuac</t>
@@ -4254,6 +5579,11 @@
       </c>
     </row>
     <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B291" t="inlineStr">
         <is>
           <t>Gutiérrez Zamora</t>
@@ -4267,9 +5597,14 @@
       </c>
     </row>
     <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>Hueyapan de Ocampo</t>
+          <t>Hueyapan De Ocampo</t>
         </is>
       </c>
       <c r="C292">
@@ -4280,9 +5615,14 @@
       </c>
     </row>
     <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>Ignacio de la Llave</t>
+          <t>Ignacio De La Llave</t>
         </is>
       </c>
       <c r="C293">
@@ -4293,6 +5633,11 @@
       </c>
     </row>
     <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B294" t="inlineStr">
         <is>
           <t>Isla</t>
@@ -4306,9 +5651,14 @@
       </c>
     </row>
     <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>Ixhuatlán de Madero</t>
+          <t>Ixhuatlán De Madero</t>
         </is>
       </c>
       <c r="C295">
@@ -4319,6 +5669,11 @@
       </c>
     </row>
     <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B296" t="inlineStr">
         <is>
           <t>Jamapa</t>
@@ -4332,6 +5687,11 @@
       </c>
     </row>
     <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B297" t="inlineStr">
         <is>
           <t>Jesús Carranza</t>
@@ -4345,9 +5705,14 @@
       </c>
     </row>
     <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>Martínez de la Torre</t>
+          <t>Martínez De La Torre</t>
         </is>
       </c>
       <c r="C298">
@@ -4358,6 +5723,11 @@
       </c>
     </row>
     <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B299" t="inlineStr">
         <is>
           <t>Minatitlán</t>
@@ -4371,6 +5741,11 @@
       </c>
     </row>
     <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B300" t="inlineStr">
         <is>
           <t>Misantla</t>
@@ -4384,6 +5759,11 @@
       </c>
     </row>
     <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B301" t="inlineStr">
         <is>
           <t>Omealca</t>
@@ -4397,6 +5777,11 @@
       </c>
     </row>
     <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B302" t="inlineStr">
         <is>
           <t>Papantla</t>
@@ -4410,6 +5795,11 @@
       </c>
     </row>
     <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B303" t="inlineStr">
         <is>
           <t>Playa Vicente</t>
@@ -4423,9 +5813,14 @@
       </c>
     </row>
     <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>Poza Rica de Hidalgo</t>
+          <t>Poza Rica De Hidalgo</t>
         </is>
       </c>
       <c r="C304">
@@ -4436,6 +5831,11 @@
       </c>
     </row>
     <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B305" t="inlineStr">
         <is>
           <t>San Andrés Tuxtla</t>
@@ -4449,6 +5849,11 @@
       </c>
     </row>
     <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B306" t="inlineStr">
         <is>
           <t>Santiago Tuxtla</t>
@@ -4462,9 +5867,14 @@
       </c>
     </row>
     <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>Soledad de Doblado</t>
+          <t>Soledad De Doblado</t>
         </is>
       </c>
       <c r="C307">
@@ -4475,6 +5885,11 @@
       </c>
     </row>
     <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B308" t="inlineStr">
         <is>
           <t>Tantoyuca</t>
@@ -4488,6 +5903,11 @@
       </c>
     </row>
     <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B309" t="inlineStr">
         <is>
           <t>Tierra Blanca</t>
@@ -4501,6 +5921,11 @@
       </c>
     </row>
     <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B310" t="inlineStr">
         <is>
           <t>Tlalixcoyan</t>
@@ -4514,6 +5939,11 @@
       </c>
     </row>
     <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B311" t="inlineStr">
         <is>
           <t>Tres Valles</t>
@@ -4527,6 +5957,11 @@
       </c>
     </row>
     <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B312" t="inlineStr">
         <is>
           <t>Tuxpan</t>
@@ -4540,6 +5975,11 @@
       </c>
     </row>
     <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B313" t="inlineStr">
         <is>
           <t>Veracruz</t>
@@ -4553,6 +5993,11 @@
       </c>
     </row>
     <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B314" t="inlineStr">
         <is>
           <t>Total</t>
@@ -4584,6 +6029,11 @@
       </c>
     </row>
     <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>Yucatán</t>
+        </is>
+      </c>
       <c r="B316" t="inlineStr">
         <is>
           <t>Total</t>
@@ -4615,6 +6065,11 @@
       </c>
     </row>
     <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B318" t="inlineStr">
         <is>
           <t>Pinos</t>
@@ -4628,6 +6083,11 @@
       </c>
     </row>
     <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B319" t="inlineStr">
         <is>
           <t>Río Grande</t>
@@ -4641,6 +6101,11 @@
       </c>
     </row>
     <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B320" t="inlineStr">
         <is>
           <t>Sain Alto</t>
@@ -4654,6 +6119,11 @@
       </c>
     </row>
     <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B321" t="inlineStr">
         <is>
           <t>Villanueva</t>
@@ -4667,6 +6137,11 @@
       </c>
     </row>
     <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B322" t="inlineStr">
         <is>
           <t>Total</t>
@@ -4690,41 +6165,6 @@
       </c>
       <c r="D323">
         <v>1</v>
-      </c>
-    </row>
-    <row r="325">
-      <c r="B325" t="inlineStr">
-        <is>
-          <t>Tamaño de la muestra: 497,795</t>
-        </is>
-      </c>
-    </row>
-    <row r="326">
-      <c r="B326" t="inlineStr">
-        <is>
-          <t>Fuente: Expedición de Matrículas Consulares de Alta Seguridad en los Consulados de México en E.E.U.U.</t>
-        </is>
-      </c>
-    </row>
-    <row r="327">
-      <c r="B327" t="inlineStr">
-        <is>
-          <t>Elaborado por: Análisis de Información, Instituto de los Mexicanos en el Exterior</t>
-        </is>
-      </c>
-    </row>
-    <row r="328">
-      <c r="B328" t="inlineStr">
-        <is>
-          <t>Secretaría de Relaciones Exteriores</t>
-        </is>
-      </c>
-    </row>
-    <row r="329">
-      <c r="B329" t="inlineStr">
-        <is>
-          <t>Octubre de 2021</t>
-        </is>
       </c>
     </row>
   </sheetData>
